--- a/public/magnolia/special.xlsx
+++ b/public/magnolia/special.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/magnolia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE5187A-8C26-8748-B855-53B701E184DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFE169A-52A7-4040-995E-5653229D44A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="600" windowWidth="17420" windowHeight="16260" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="600" windowWidth="17420" windowHeight="16260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Maslenitsa" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="80">
   <si>
     <t>title_ru</t>
   </si>
@@ -130,24 +130,6 @@
   </si>
   <si>
     <t>გرمული სასმელი ვაშლის გემოთი და სანელებლებით.</t>
-  </si>
-  <si>
-    <t>Клюквенная Матча</t>
-  </si>
-  <si>
-    <t>Cranberry Matcha</t>
-  </si>
-  <si>
-    <t>წითელი მოცხარის მატჩა</t>
-  </si>
-  <si>
-    <t>Освежающий чай с ягодной кислинкой и травянистой ноткой.</t>
-  </si>
-  <si>
-    <t>Refreshing tea with berry tartness and herbal notes.</t>
-  </si>
-  <si>
-    <t>გამაგრილებელი ჩაი მსუბუქი კენკრის მჟავით და მცენარეული ნოტებით.</t>
   </si>
   <si>
     <t>Глинтвейн</t>
@@ -901,13 +883,13 @@
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="19">
       <c r="A2" s="13" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13">
@@ -921,19 +903,19 @@
         <v>pancake cheeseburger</v>
       </c>
       <c r="J2" s="6" t="str">
-        <f t="shared" ref="J2:J14" si="0">LOWER($B2)&amp;"_"&amp;2</f>
+        <f t="shared" ref="J2:J8" si="0">LOWER($B2)&amp;"_"&amp;2</f>
         <v>pancake cheeseburger_2</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="1" customFormat="1" ht="19">
       <c r="A3" s="14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13">
@@ -943,7 +925,7 @@
       <c r="G3" s="14"/>
       <c r="H3" s="14"/>
       <c r="I3" s="6" t="str">
-        <f t="shared" ref="I2:I3" si="1">LOWER($B3)</f>
+        <f t="shared" ref="I3" si="1">LOWER($B3)</f>
         <v>pancakes with salmon and cucumber</v>
       </c>
       <c r="J3" s="6" t="str">
@@ -953,13 +935,13 @@
     </row>
     <row r="4" spans="1:13" s="1" customFormat="1" ht="19">
       <c r="A4" s="14" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="D4" s="13"/>
       <c r="E4" s="13">
@@ -979,13 +961,13 @@
     </row>
     <row r="5" spans="1:13" s="5" customFormat="1" ht="19">
       <c r="A5" s="14" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13">
@@ -1007,13 +989,13 @@
     </row>
     <row r="6" spans="1:13" s="5" customFormat="1" ht="19">
       <c r="A6" s="17" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13">
@@ -1033,13 +1015,13 @@
     </row>
     <row r="7" spans="1:13" s="5" customFormat="1" ht="19">
       <c r="A7" s="17" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13">
@@ -1059,13 +1041,13 @@
     </row>
     <row r="8" spans="1:13" s="5" customFormat="1" ht="19">
       <c r="A8" s="17" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13">
@@ -5126,7 +5108,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M1003"/>
+  <dimension ref="A1:J1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -5138,7 +5120,7 @@
     <col min="12" max="13" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="1" customFormat="1" ht="19">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5170,7 +5152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="19">
+    <row r="2" spans="1:10" s="1" customFormat="1" ht="19">
       <c r="A2" s="13" t="s">
         <v>13</v>
       </c>
@@ -5202,7 +5184,7 @@
         <v>maple raf_2</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="19">
+    <row r="3" spans="1:10" s="1" customFormat="1" ht="19">
       <c r="A3" s="14" t="s">
         <v>19</v>
       </c>
@@ -5234,7 +5216,7 @@
         <v>cherry mokka_2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" s="1" customFormat="1" ht="19">
+    <row r="4" spans="1:10" s="1" customFormat="1" ht="19">
       <c r="A4" s="14" t="s">
         <v>25</v>
       </c>
@@ -5266,11 +5248,11 @@
         <v>apple grog_2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="5" customFormat="1" ht="19">
+    <row r="5" spans="1:10" s="5" customFormat="1" ht="19">
       <c r="A5" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>32</v>
       </c>
       <c r="C5" s="14" t="s">
@@ -5278,33 +5260,31 @@
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="14" t="s">
         <v>35</v>
       </c>
       <c r="H5" s="14" t="s">
         <v>36</v>
       </c>
       <c r="I5" s="6" t="str">
-        <f t="shared" ref="I5:I14" si="2">LOWER($B5)</f>
-        <v>cranberry matcha</v>
+        <f t="shared" ref="I5:I13" si="2">LOWER($B5)</f>
+        <v>mulled wine</v>
       </c>
       <c r="J5" s="6" t="str">
-        <f t="shared" ref="J5:J14" si="3">LOWER($B5)&amp;"_"&amp;2</f>
-        <v>cranberry matcha_2</v>
-      </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-    </row>
-    <row r="6" spans="1:13" s="5" customFormat="1" ht="19">
+        <f t="shared" ref="J5:J13" si="3">LOWER($B5)&amp;"_"&amp;2</f>
+        <v>mulled wine_2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="5" customFormat="1" ht="19">
       <c r="A6" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="14" t="s">
@@ -5312,7 +5292,7 @@
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F6" s="14" t="s">
         <v>40</v>
@@ -5325,21 +5305,21 @@
       </c>
       <c r="I6" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>mulled wine</v>
+        <v>cranberry &amp; spices</v>
       </c>
       <c r="J6" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>mulled wine_2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="5" customFormat="1" ht="19">
-      <c r="A7" s="14" t="s">
+        <v>cranberry &amp; spices_2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="5" customFormat="1" ht="19">
+      <c r="A7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>45</v>
       </c>
       <c r="D7" s="13"/>
@@ -5357,21 +5337,21 @@
       </c>
       <c r="I7" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>cranberry &amp; spices</v>
+        <v>raspberry &amp; herbs</v>
       </c>
       <c r="J7" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>cranberry &amp; spices_2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="5" customFormat="1" ht="19">
-      <c r="A8" s="13" t="s">
+        <v>raspberry &amp; herbs_2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="5" customFormat="1" ht="19">
+      <c r="A8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D8" s="13"/>
@@ -5381,7 +5361,7 @@
       <c r="F8" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="15" t="s">
         <v>53</v>
       </c>
       <c r="H8" s="14" t="s">
@@ -5389,54 +5369,37 @@
       </c>
       <c r="I8" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>raspberry &amp; herbs</v>
+        <v>sea buckthorn &amp; rosemary</v>
       </c>
       <c r="J8" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>raspberry &amp; herbs_2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" s="5" customFormat="1" ht="19">
-      <c r="A9" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>57</v>
-      </c>
+        <v>sea buckthorn &amp; rosemary_2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
       <c r="D9" s="13"/>
-      <c r="E9" s="13">
-        <v>10</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>60</v>
-      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="10"/>
       <c r="I9" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>sea buckthorn &amp; rosemary</v>
+        <v/>
       </c>
       <c r="J9" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>sea buckthorn &amp; rosemary_2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" customHeight="1">
+        <v>_2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="13"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="10"/>
       <c r="I10" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5446,7 +5409,7 @@
         <v>_2</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" customHeight="1">
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -5461,7 +5424,7 @@
         <v>_2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.75" customHeight="1">
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -5476,7 +5439,7 @@
         <v>_2</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -5491,26 +5454,15 @@
         <v>_2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="4"/>
-      <c r="I14" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J14" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>_2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15.75" customHeight="1">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
       <c r="D15" s="11"/>
       <c r="E15" s="11"/>
     </row>
-    <row r="16" spans="1:13" ht="15.75" customHeight="1">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
       <c r="D16" s="11"/>
       <c r="E16" s="11"/>
     </row>
@@ -5646,7 +5598,7 @@
       <c r="D49" s="11"/>
       <c r="E49" s="11"/>
     </row>
-    <row r="50" spans="4:5" ht="15.75" customHeight="1">
+    <row r="50" spans="4:5">
       <c r="D50" s="11"/>
       <c r="E50" s="11"/>
     </row>
@@ -9457,10 +9409,6 @@
     <row r="1002" spans="4:5">
       <c r="D1002" s="11"/>
       <c r="E1002" s="11"/>
-    </row>
-    <row r="1003" spans="4:5">
-      <c r="D1003" s="11"/>
-      <c r="E1003" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -9499,24 +9447,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="16" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1"/>

--- a/public/magnolia/special.xlsx
+++ b/public/magnolia/special.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/magnolia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8F8689C-5325-6943-9DF9-A4AFC2DB27BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46CDEBE-0507-1A48-90B2-ACC1F3718BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="600" windowWidth="17420" windowHeight="16260" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="120" yWindow="600" windowWidth="17420" windowHeight="16260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Special " sheetId="3" r:id="rId1"/>
+    <sheet name="Special" sheetId="3" r:id="rId1"/>
     <sheet name="Seasonal Drinks" sheetId="1" r:id="rId2"/>
     <sheet name="catalogs" sheetId="2" r:id="rId3"/>
   </sheets>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
   <si>
     <t>title_ru</t>
   </si>
@@ -112,42 +112,6 @@
   </si>
   <si>
     <t>ტკბილი ყავა ნაზი შოკოლადის სიმწარით და კაშკაშა ალუბლის არომატით.</t>
-  </si>
-  <si>
-    <t>Яблочный Грог</t>
-  </si>
-  <si>
-    <t>Apple Grog</t>
-  </si>
-  <si>
-    <t>ვაშლის გროგი</t>
-  </si>
-  <si>
-    <t>Тёплый напиток с яблочным вкусом и пряностями.</t>
-  </si>
-  <si>
-    <t>Warm drink with apple flavor and spices.</t>
-  </si>
-  <si>
-    <t>გرمული სასმელი ვაშლის გემოთი და სანელებლებით.</t>
-  </si>
-  <si>
-    <t>Глинтвейн</t>
-  </si>
-  <si>
-    <t>Mulled Wine</t>
-  </si>
-  <si>
-    <t>გლინტვეინი</t>
-  </si>
-  <si>
-    <t>Тёплый пряный напиток с нотами фруктов и специй.</t>
-  </si>
-  <si>
-    <t>Warm spiced drink with fruity notes.</t>
-  </si>
-  <si>
-    <t>გرمული, სანელებლებით და ხილის ნოტებით.</t>
   </si>
   <si>
     <t>Клюква &amp; Специи</t>
@@ -827,13 +791,13 @@
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="19">
       <c r="A2" s="12" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12">
@@ -853,13 +817,13 @@
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="19">
       <c r="A3" s="13" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12">
@@ -879,13 +843,13 @@
     </row>
     <row r="4" spans="1:10" s="5" customFormat="1" ht="19">
       <c r="A4" s="16" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12">
@@ -4946,7 +4910,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J1002"/>
+  <dimension ref="A1:J1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="21.83203125" customWidth="1"/>
@@ -5018,7 +4982,7 @@
         <v>maple raf</v>
       </c>
       <c r="J2" s="6" t="str">
-        <f t="shared" ref="J2:J4" si="1">LOWER($B2)&amp;"_"&amp;2</f>
+        <f t="shared" ref="J2:J3" si="1">LOWER($B2)&amp;"_"&amp;2</f>
         <v>maple raf_2</v>
       </c>
     </row>
@@ -5054,11 +5018,11 @@
         <v>cherry mokka_2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" s="1" customFormat="1" ht="19">
+    <row r="4" spans="1:10" s="5" customFormat="1" ht="19">
       <c r="A4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>26</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -5066,9 +5030,9 @@
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12">
-        <v>16</v>
-      </c>
-      <c r="F4" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>28</v>
       </c>
       <c r="G4" s="13" t="s">
@@ -5078,27 +5042,27 @@
         <v>30</v>
       </c>
       <c r="I4" s="6" t="str">
-        <f>LOWER($B4)</f>
-        <v>apple grog</v>
+        <f t="shared" ref="I4:I11" si="2">LOWER($B4)</f>
+        <v>cranberry &amp; spices</v>
       </c>
       <c r="J4" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>apple grog_2</v>
+        <f t="shared" ref="J4:J11" si="3">LOWER($B4)&amp;"_"&amp;2</f>
+        <v>cranberry &amp; spices_2</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="5" customFormat="1" ht="19">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F5" s="13" t="s">
         <v>34</v>
@@ -5110,12 +5074,12 @@
         <v>36</v>
       </c>
       <c r="I5" s="6" t="str">
-        <f t="shared" ref="I5:I13" si="2">LOWER($B5)</f>
-        <v>mulled wine</v>
+        <f t="shared" si="2"/>
+        <v>raspberry &amp; herbs</v>
       </c>
       <c r="J5" s="6" t="str">
-        <f t="shared" ref="J5:J13" si="3">LOWER($B5)&amp;"_"&amp;2</f>
-        <v>mulled wine_2</v>
+        <f t="shared" si="3"/>
+        <v>raspberry &amp; herbs_2</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="5" customFormat="1" ht="19">
@@ -5135,7 +5099,7 @@
       <c r="F6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="14" t="s">
         <v>41</v>
       </c>
       <c r="H6" s="13" t="s">
@@ -5143,75 +5107,44 @@
       </c>
       <c r="I6" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>cranberry &amp; spices</v>
+        <v>sea buckthorn &amp; rosemary</v>
       </c>
       <c r="J6" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>cranberry &amp; spices_2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" s="5" customFormat="1" ht="19">
-      <c r="A7" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>45</v>
-      </c>
+        <v>sea buckthorn &amp; rosemary_2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="12"/>
-      <c r="E7" s="12">
-        <v>10</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>48</v>
-      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="9"/>
       <c r="I7" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>raspberry &amp; herbs</v>
+        <v/>
       </c>
       <c r="J7" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>raspberry &amp; herbs_2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" s="5" customFormat="1" ht="19">
-      <c r="A8" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>51</v>
-      </c>
+        <v>_2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
       <c r="D8" s="12"/>
-      <c r="E8" s="12">
-        <v>10</v>
-      </c>
-      <c r="F8" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>54</v>
-      </c>
+      <c r="E8" s="4"/>
       <c r="I8" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>sea buckthorn &amp; rosemary</v>
+        <v/>
       </c>
       <c r="J8" s="6" t="str">
         <f t="shared" si="3"/>
-        <v>sea buckthorn &amp; rosemary_2</v>
+        <v>_2</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1">
@@ -5220,9 +5153,6 @@
       <c r="C9" s="3"/>
       <c r="D9" s="12"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="9"/>
       <c r="I9" s="6" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -5263,34 +5193,12 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="4"/>
-      <c r="I12" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J12" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>_2</v>
-      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="4"/>
-      <c r="I13" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J13" s="6" t="str">
-        <f t="shared" si="3"/>
-        <v>_2</v>
-      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:10" ht="15.75" customHeight="1">
       <c r="D14" s="10"/>
@@ -5428,11 +5336,11 @@
       <c r="D47" s="10"/>
       <c r="E47" s="10"/>
     </row>
-    <row r="48" spans="4:5" ht="15.75" customHeight="1">
+    <row r="48" spans="4:5">
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
     </row>
-    <row r="49" spans="4:5" ht="15.75" customHeight="1">
+    <row r="49" spans="4:5">
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
     </row>
@@ -9239,14 +9147,6 @@
     <row r="1000" spans="4:5">
       <c r="D1000" s="10"/>
       <c r="E1000" s="10"/>
-    </row>
-    <row r="1001" spans="4:5">
-      <c r="D1001" s="10"/>
-      <c r="E1001" s="10"/>
-    </row>
-    <row r="1002" spans="4:5">
-      <c r="D1002" s="10"/>
-      <c r="E1002" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
@@ -9285,24 +9185,24 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="15" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1"/>

--- a/public/magnolia/special.xlsx
+++ b/public/magnolia/special.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/magnolia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B46CDEBE-0507-1A48-90B2-ACC1F3718BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF31294-68D4-2B46-B12D-CA5B976F7F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="600" windowWidth="17420" windowHeight="16260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="980" windowWidth="17420" windowHeight="16260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Special" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
   <si>
     <t>title_ru</t>
   </si>
@@ -206,12 +206,21 @@
   <si>
     <t>Special</t>
   </si>
+  <si>
+    <t>Креп Сюзет</t>
+  </si>
+  <si>
+    <t>კრეპ სუზეტი</t>
+  </si>
+  <si>
+    <t>crêpe suzette</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -318,6 +327,13 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -339,7 +355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -363,6 +379,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -811,7 +828,7 @@
         <v>pancake cheeseburger</v>
       </c>
       <c r="J2" s="6" t="str">
-        <f t="shared" ref="J2:J4" si="0">LOWER($B2)&amp;"_"&amp;2</f>
+        <f t="shared" ref="J2:J5" si="0">LOWER($B2)&amp;"_"&amp;2</f>
         <v>pancake cheeseburger_2</v>
       </c>
     </row>
@@ -868,16 +885,30 @@
       </c>
     </row>
     <row r="5" spans="1:10" s="5" customFormat="1" ht="19">
-      <c r="A5" s="13"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
+      <c r="A5" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>57</v>
+      </c>
       <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
+      <c r="E5" s="12">
+        <v>14</v>
+      </c>
       <c r="F5" s="13"/>
       <c r="G5" s="14"/>
       <c r="H5" s="13"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
+      <c r="I5" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>crêpe suzette</v>
+      </c>
+      <c r="J5" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>crêpe suzette_2</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
       <c r="A6" s="3"/>

--- a/public/magnolia/special.xlsx
+++ b/public/magnolia/special.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elizaveta/Desktop/projects/sage/GkirillS.github.io/public/magnolia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF31294-68D4-2B46-B12D-CA5B976F7F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C1DBFCE-ABA4-3640-BD15-F48CE6476A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="980" windowWidth="17420" windowHeight="16260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="600" windowWidth="17420" windowHeight="16260" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Special" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
   <si>
     <t>title_ru</t>
   </si>
@@ -174,46 +174,10 @@
     <t>Сезонные напитки</t>
   </si>
   <si>
-    <t>Блин чизбургер</t>
-  </si>
-  <si>
-    <t>პანკეიქების ჩიზბურგერი</t>
-  </si>
-  <si>
-    <t>Блины с лососем, крем чизом и огурцом</t>
-  </si>
-  <si>
-    <t>ბლინები ლოსოსით, კრემ-ჩიზით და კიტრით</t>
-  </si>
-  <si>
-    <t>Блины со сгущенкой и бананом</t>
-  </si>
-  <si>
-    <t>ბლინები შესქელებული რძით და ბანანით</t>
-  </si>
-  <si>
-    <t>Pancakes with salmon and cucumber</t>
-  </si>
-  <si>
-    <t>Pancake cheeseburger</t>
-  </si>
-  <si>
-    <t>Pancakes with condensed milk</t>
-  </si>
-  <si>
     <t>Спешл</t>
   </si>
   <si>
     <t>Special</t>
-  </si>
-  <si>
-    <t>Креп Сюзет</t>
-  </si>
-  <si>
-    <t>კრეპ სუზეტი</t>
-  </si>
-  <si>
-    <t>crêpe suzette</t>
   </si>
 </sst>
 </file>
@@ -807,107 +771,75 @@
       </c>
     </row>
     <row r="2" spans="1:10" s="1" customFormat="1" ht="19">
-      <c r="A2" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>46</v>
-      </c>
+      <c r="A2" s="12"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
       <c r="D2" s="12"/>
-      <c r="E2" s="12">
-        <v>18</v>
-      </c>
+      <c r="E2" s="12"/>
       <c r="F2" s="13"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
       <c r="I2" s="6" t="str">
         <f>LOWER($B2)</f>
-        <v>pancake cheeseburger</v>
+        <v/>
       </c>
       <c r="J2" s="6" t="str">
         <f t="shared" ref="J2:J5" si="0">LOWER($B2)&amp;"_"&amp;2</f>
-        <v>pancake cheeseburger_2</v>
+        <v>_2</v>
       </c>
     </row>
     <row r="3" spans="1:10" s="1" customFormat="1" ht="19">
-      <c r="A3" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>48</v>
-      </c>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="17"/>
       <c r="D3" s="12"/>
-      <c r="E3" s="12">
-        <v>18</v>
-      </c>
+      <c r="E3" s="12"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
       <c r="I3" s="6" t="str">
         <f t="shared" ref="I3" si="1">LOWER($B3)</f>
-        <v>pancakes with salmon and cucumber</v>
+        <v/>
       </c>
       <c r="J3" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>pancakes with salmon and cucumber_2</v>
+        <v>_2</v>
       </c>
     </row>
     <row r="4" spans="1:10" s="5" customFormat="1" ht="19">
-      <c r="A4" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>50</v>
-      </c>
+      <c r="A4" s="16"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
       <c r="D4" s="12"/>
-      <c r="E4" s="12">
-        <v>14</v>
-      </c>
+      <c r="E4" s="12"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="6" t="str">
         <f t="shared" ref="I4:I10" si="2">LOWER($B4)</f>
-        <v>pancakes with condensed milk</v>
+        <v/>
       </c>
       <c r="J4" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>pancakes with condensed milk_2</v>
+        <v>_2</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="5" customFormat="1" ht="19">
-      <c r="A5" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>57</v>
-      </c>
+      <c r="A5" s="13"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="12"/>
-      <c r="E5" s="12">
-        <v>14</v>
-      </c>
+      <c r="E5" s="12"/>
       <c r="F5" s="13"/>
       <c r="G5" s="14"/>
       <c r="H5" s="13"/>
       <c r="I5" s="6" t="str">
         <f t="shared" si="2"/>
-        <v>crêpe suzette</v>
+        <v/>
       </c>
       <c r="J5" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>crêpe suzette_2</v>
+        <v>_2</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1">
@@ -9216,13 +9148,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="15" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:3">
